--- a/tame_output/MOZAIC/bt/btc_vs_alt_20230724.xlsx
+++ b/tame_output/MOZAIC/bt/btc_vs_alt_20230724.xlsx
@@ -52690,19 +52690,19 @@
         <v>1.628910960935361</v>
       </c>
       <c r="D2010" t="n">
-        <v>1.497697775882719</v>
+        <v>1.500577031944586</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.56330436840904</v>
+        <v>1.564743996439974</v>
       </c>
       <c r="F2010" t="n">
         <v>4.838309193352922</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.78582391933187</v>
+        <v>4.786975621756617</v>
       </c>
       <c r="H2010" t="n">
-        <v>4.812066556342379</v>
+        <v>4.812642407554752</v>
       </c>
     </row>
     <row r="2011">
@@ -52713,22 +52713,22 @@
         <v>4.191742345714202</v>
       </c>
       <c r="C2011" t="n">
-        <v>1.621906489069275</v>
+        <v>1.620402366596147</v>
       </c>
       <c r="D2011" t="n">
-        <v>1.491558731914342</v>
+        <v>1.495005225715913</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.556732610491809</v>
+        <v>1.55770379615603</v>
       </c>
       <c r="F2011" t="n">
-        <v>4.840504941341921</v>
+        <v>4.83990329235267</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.788365838479953</v>
+        <v>4.789744436000581</v>
       </c>
       <c r="H2011" t="n">
-        <v>4.81443538991092</v>
+        <v>4.814823864176608</v>
       </c>
     </row>
     <row r="2012">
@@ -52739,22 +52739,22 @@
         <v>4.1736787626571</v>
       </c>
       <c r="C2012" t="n">
-        <v>1.63008700856969</v>
+        <v>1.631377146292433</v>
       </c>
       <c r="D2012" t="n">
-        <v>1.500438137040519</v>
+        <v>1.504453722749161</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.565262572805104</v>
+        <v>1.567915434520797</v>
       </c>
       <c r="F2012" t="n">
-        <v>4.825713566084985</v>
+        <v>4.826229621174082</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.773854017473321</v>
+        <v>4.775460251756779</v>
       </c>
       <c r="H2012" t="n">
-        <v>4.799783791779136</v>
+        <v>4.800844936465413</v>
       </c>
     </row>
     <row r="2013">
@@ -52765,22 +52765,22 @@
         <v>4.155481419350962</v>
       </c>
       <c r="C2013" t="n">
-        <v>1.624218438856666</v>
+        <v>1.625205740375742</v>
       </c>
       <c r="D2013" t="n">
-        <v>1.497461362185514</v>
+        <v>1.501250416261587</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.56083990052109</v>
+        <v>1.563228078318665</v>
       </c>
       <c r="F2013" t="n">
-        <v>4.805168794893637</v>
+        <v>4.805563715501267</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.754465964225181</v>
+        <v>4.755981585855611</v>
       </c>
       <c r="H2013" t="n">
-        <v>4.779817379559392</v>
+        <v>4.780772650678422</v>
       </c>
     </row>
     <row r="2014">
@@ -52791,22 +52791,22 @@
         <v>4.146824167407236</v>
       </c>
       <c r="C2014" t="n">
-        <v>1.631345348937861</v>
+        <v>1.6355808814674</v>
       </c>
       <c r="D2014" t="n">
-        <v>1.508499828267525</v>
+        <v>1.512814657692838</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.569922588602693</v>
+        <v>1.574197769580119</v>
       </c>
       <c r="F2014" t="n">
-        <v>4.79936230698239</v>
+        <v>4.801056519994205</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.75022409871426</v>
+        <v>4.751950030484386</v>
       </c>
       <c r="H2014" t="n">
-        <v>4.774793202848308</v>
+        <v>4.776503275239278</v>
       </c>
     </row>
     <row r="2015">
@@ -52817,22 +52817,22 @@
         <v>4.134426248999913</v>
       </c>
       <c r="C2015" t="n">
-        <v>1.624747148511763</v>
+        <v>1.630144200439621</v>
       </c>
       <c r="D2015" t="n">
-        <v>1.507326110042839</v>
+        <v>1.512369895835015</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.566036629277301</v>
+        <v>1.571257048137318</v>
       </c>
       <c r="F2015" t="n">
-        <v>4.784325108404627</v>
+        <v>4.78648392917577</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.737356693017063</v>
+        <v>4.739374207333933</v>
       </c>
       <c r="H2015" t="n">
-        <v>4.760840900710828</v>
+        <v>4.762929068254834</v>
       </c>
     </row>
     <row r="2016">
@@ -52843,22 +52843,22 @@
         <v>4.154885080289795</v>
       </c>
       <c r="C2016" t="n">
-        <v>1.618743008175947</v>
+        <v>1.624940803301757</v>
       </c>
       <c r="D2016" t="n">
-        <v>1.502640388094984</v>
+        <v>1.50729229024829</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.560691698135465</v>
+        <v>1.566116546775024</v>
       </c>
       <c r="F2016" t="n">
-        <v>4.802382283560183</v>
+        <v>4.804861401610506</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.755941235527803</v>
+        <v>4.757801996389125</v>
       </c>
       <c r="H2016" t="n">
-        <v>4.779161759543975</v>
+        <v>4.781331698999798</v>
       </c>
     </row>
     <row r="2017">
@@ -52869,22 +52869,22 @@
         <v>4.145310928803405</v>
       </c>
       <c r="C2017" t="n">
-        <v>1.612513147465642</v>
+        <v>1.615348572983637</v>
       </c>
       <c r="D2017" t="n">
-        <v>1.496020638126043</v>
+        <v>1.49907404424947</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.554266892795843</v>
+        <v>1.557211308616554</v>
       </c>
       <c r="F2017" t="n">
-        <v>4.790316187789672</v>
+        <v>4.791450357996869</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.743719184053838</v>
+        <v>4.744940546503208</v>
       </c>
       <c r="H2017" t="n">
-        <v>4.767017685921737</v>
+        <v>4.768195452250021</v>
       </c>
     </row>
     <row r="2018">
@@ -52895,22 +52895,22 @@
         <v>4.133461272061444</v>
       </c>
       <c r="C2018" t="n">
-        <v>1.618009941576672</v>
+        <v>1.620845367094667</v>
       </c>
       <c r="D2018" t="n">
-        <v>1.49396824955316</v>
+        <v>1.496776701956149</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.555989095564916</v>
+        <v>1.558811034525408</v>
       </c>
       <c r="F2018" t="n">
-        <v>4.780665248692123</v>
+        <v>4.78179941889932</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.731048571882723</v>
+        <v>4.732171952843918</v>
       </c>
       <c r="H2018" t="n">
-        <v>4.755856910287406</v>
+        <v>4.756985685871602</v>
       </c>
     </row>
     <row r="2019">
@@ -52921,22 +52921,22 @@
         <v>4.136457215367947</v>
       </c>
       <c r="C2019" t="n">
-        <v>1.616526570328183</v>
+        <v>1.619361995846178</v>
       </c>
       <c r="D2019" t="n">
-        <v>1.496849263823538</v>
+        <v>1.501385713296198</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.556687917075861</v>
+        <v>1.560373854571188</v>
       </c>
       <c r="F2019" t="n">
-        <v>4.78306784349923</v>
+        <v>4.784202013706427</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.735196920897376</v>
+        <v>4.73701150068644</v>
       </c>
       <c r="H2019" t="n">
-        <v>4.759132382198286</v>
+        <v>4.760606757196416</v>
       </c>
     </row>
     <row r="2020">
@@ -52947,22 +52947,22 @@
         <v>4.145916630926916</v>
       </c>
       <c r="C2020" t="n">
-        <v>1.613817347891047</v>
+        <v>1.616652773409042</v>
       </c>
       <c r="D2020" t="n">
-        <v>1.498618426716295</v>
+        <v>1.503407631599774</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.556217887303671</v>
+        <v>1.560030202504408</v>
       </c>
       <c r="F2020" t="n">
-        <v>4.791443570083345</v>
+        <v>4.792577740290541</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.745364001613448</v>
+        <v>4.747279683566839</v>
       </c>
       <c r="H2020" t="n">
-        <v>4.768403785848379</v>
+        <v>4.769928711928673</v>
       </c>
     </row>
     <row r="2021">
@@ -52973,22 +52973,22 @@
         <v>4.141606803092691</v>
       </c>
       <c r="C2021" t="n">
-        <v>1.614719948726981</v>
+        <v>1.617555374244976</v>
       </c>
       <c r="D2021" t="n">
-        <v>1.509818294393489</v>
+        <v>1.514959958168122</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.562269121560235</v>
+        <v>1.566257666206549</v>
       </c>
       <c r="F2021" t="n">
-        <v>4.787494782583495</v>
+        <v>4.788628952790691</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.745534120850101</v>
+        <v>4.747590786359954</v>
       </c>
       <c r="H2021" t="n">
-        <v>4.76651445171678</v>
+        <v>4.768109869575304</v>
       </c>
     </row>
     <row r="2022">
@@ -52999,22 +52999,22 @@
         <v>4.154894226074353</v>
       </c>
       <c r="C2022" t="n">
-        <v>1.535817872658521</v>
+        <v>1.538653298176516</v>
       </c>
       <c r="D2022" t="n">
-        <v>1.451524074133868</v>
+        <v>1.452268726141252</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.493670973396195</v>
+        <v>1.495461012158884</v>
       </c>
       <c r="F2022" t="n">
-        <v>4.769221375137772</v>
+        <v>4.770355545344969</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.735503855727914</v>
+        <v>4.735801716530867</v>
       </c>
       <c r="H2022" t="n">
-        <v>4.752362615432825</v>
+        <v>4.7530786309379</v>
       </c>
     </row>
   </sheetData>
